--- a/AT.xlsx
+++ b/AT.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10302"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10308"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2FEE39EF-15E1-2348-B016-1B607A9EB0C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99A2973C-2D04-D745-A72E-A334E236D9B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -50,7 +50,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="66">
   <si>
     <t>Astar Boyu</t>
   </si>
@@ -245,6 +245,9 @@
   </si>
   <si>
     <t>KU_</t>
+  </si>
+  <si>
+    <t>deneme</t>
   </si>
 </sst>
 </file>
@@ -1981,7 +1984,9 @@
       </c>
       <c r="D12" s="3"/>
       <c r="E12" s="3"/>
-      <c r="F12" s="3"/>
+      <c r="F12" s="3" t="s">
+        <v>65</v>
+      </c>
       <c r="G12" s="3"/>
       <c r="H12" s="3"/>
       <c r="I12" s="3"/>
@@ -2070,7 +2075,9 @@
       <c r="D15" s="2"/>
       <c r="E15" s="2"/>
       <c r="F15" s="2"/>
-      <c r="G15" s="2"/>
+      <c r="G15" s="2" t="s">
+        <v>65</v>
+      </c>
       <c r="H15" s="2"/>
       <c r="I15" s="2"/>
       <c r="J15" s="2"/>
@@ -2095,7 +2102,9 @@
       <c r="C16" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="D16" s="2"/>
+      <c r="D16" s="2" t="s">
+        <v>65</v>
+      </c>
       <c r="E16" s="2"/>
       <c r="F16" s="2"/>
       <c r="G16" s="2"/>

--- a/AT.xlsx
+++ b/AT.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10308"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99A2973C-2D04-D745-A72E-A334E236D9B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A470223-C93F-3040-9356-079E10840EC1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -50,7 +50,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="65">
   <si>
     <t>Astar Boyu</t>
   </si>
@@ -245,9 +245,6 @@
   </si>
   <si>
     <t>KU_</t>
-  </si>
-  <si>
-    <t>deneme</t>
   </si>
 </sst>
 </file>
@@ -1984,9 +1981,7 @@
       </c>
       <c r="D12" s="3"/>
       <c r="E12" s="3"/>
-      <c r="F12" s="3" t="s">
-        <v>65</v>
-      </c>
+      <c r="F12" s="3"/>
       <c r="G12" s="3"/>
       <c r="H12" s="3"/>
       <c r="I12" s="3"/>
@@ -2075,9 +2070,7 @@
       <c r="D15" s="2"/>
       <c r="E15" s="2"/>
       <c r="F15" s="2"/>
-      <c r="G15" s="2" t="s">
-        <v>65</v>
-      </c>
+      <c r="G15" s="2"/>
       <c r="H15" s="2"/>
       <c r="I15" s="2"/>
       <c r="J15" s="2"/>
@@ -2102,9 +2095,7 @@
       <c r="C16" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="D16" s="2" t="s">
-        <v>65</v>
-      </c>
+      <c r="D16" s="2"/>
       <c r="E16" s="2"/>
       <c r="F16" s="2"/>
       <c r="G16" s="2"/>
